--- a/reports/作品列表.xlsx
+++ b/reports/作品列表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>作品名称</t>
   </si>
@@ -64,6 +64,212 @@
   </si>
   <si>
     <t>粉丝增量</t>
+  </si>
+  <si>
+    <t>你还不敢开口 打卡 700 天，见到老外还是嘴张开一半。 
+不是你菜，是没人陪你练。 
+问 AI「怎么练口语」，它甩你 10 条建议——全是废话。 
+因为你不是要 AI 教你，你是要 AI 陪你说。 
+给它一张角色卡：你是我雅思口语搭档，我 Part 3，你只用英文提问，我说错也别打断。 
+先敢说 30 分钟，比敢背 300 单词管用。 
+评论区回复 面试 / 雅思 / 日常 / 旅游，我把对应 role prompt 私发给你。 
+#AI英语  #口语练习   #学英语  #AI陪练 #AI工具</t>
+  </si>
+  <si>
+    <t>2026-07-06 09:13:00</t>
+  </si>
+  <si>
+    <t>1min-视频</t>
+  </si>
+  <si>
+    <t>公开</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>0.014493</t>
+  </si>
+  <si>
+    <t>0.208333</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.597222</t>
+  </si>
+  <si>
+    <t>4.027778</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>我只在 queue 打了一行选题后面全流程 Agent 自 做内容最烦的不是写一句钩子，是后面那一串：调研、洞察、脚本、形式、门禁、出片。 
+我现在只在 `queue/topics.yaml` 里打一行选题。后面洞察包、讨论室打分、`gate_check` 两道门——工种 scorecard 没过 90，不让配音出片；脚本 90 分，形式不过，照样退稿。 
+跑通 pipeline ≠ 能发。你现在看的这条发布包，就是这么出来的。
+#一人公司  #AI工具   #独立开发  #内容创业#短视频变现</t>
+  </si>
+  <si>
+    <t>2026-07-04 09:13:00</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0.000000</t>
+  </si>
+  <si>
+    <t>1.000000</t>
+  </si>
+  <si>
+    <t>我用 AI 把一周的活干成一天，现在它自己在帮我攒客户 一个人做老外的英文市场，我把"拉客→收邮箱→自动跟进"整条线，一天搭上线。
+留完邮箱那一刻起，欢迎信、后面十天的养熟邮件，全是系统自己一封封发——跟进我盯的时间，几乎是零。
+可第5天我一看数据傻眼了：曝光涨了，留下的却寥寥无几。
+扒了一圈才明白：不是系统的事，是内容太机器——AI 一键出的图谁都刷过，没人停。
+改成「AI 只出背景、文字我自己排」，才像活人发的，留资才开始动。
+系统能跑，内容得先像人。 
+#一人公司  #出海 #AI工具  #独立开发  #邮件营销</t>
+  </si>
+  <si>
+    <t>2026-07-03 09:13:01</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>0.025641</t>
+  </si>
+  <si>
+    <t>0.142857</t>
+  </si>
+  <si>
+    <t>0.653061</t>
+  </si>
+  <si>
+    <t>5.204082</t>
+  </si>
+  <si>
+    <t>4 周做AI内容粉丝几乎没动,但今早 3 个老板私信问我 做 AI 内容 4 周,粉丝几乎没动过。最久的一条 32 播,最少的 11 播。
+但今早,3 个实体店老板私信问我:能不能给我店里也做一套?
+你可能想笑——自己都做不起来,凭啥收钱?
+我反过来想:**我已经扑得很彻底,每个坑我都精确知道在哪。这是花钱买不到的清单。** 
+4 周,AI 全自动出片,单条不到 3 块。
+开 3 档实体店老板用:
+- ¥99/月 = 4 条小红书
+- ¥299/月 = 14 条
+- ¥599/月 = 14 条 + 每周复盘
+**14 条交付不行你说停,剩下原路退。**
+但我不知道有没有人愿意付。所以这条不是广告,是测水。
+#AI内容  #实体店运营  #降本增效  #一人公司  #AI工具</t>
+  </si>
+  <si>
+    <t>2026-07-02 09:13:00</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>散会我就走｜纪要和待办 AI 已经发群里了 散会了，同事还在写纪要，我直接走了。
+不是我摆烂——纪要和待办，群里早自动发好了。
+我那套系统全程在听：散会就出结构化纪要，每条待办谁负责、什么时候交，自动 @ 到人，到期还提醒。
+画面里开会、纪要卡、待办清单，是我把真实流程演绎给你看。
+以前开完会最烦的不是会，是会后熬夜整理、追着每个人要进度。
+现在我只管讨论拍板，记录和追办交给它。
+开会的价值是讨论，记录和追待办，根本不该是人干的活。
+这套我自己天天在用。 
+#职场 #会议纪要  #AI工具  #效率提升  #一人公司</t>
+  </si>
+  <si>
+    <t>2026-06-30 09:13:00</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>0.064516</t>
+  </si>
+  <si>
+    <t>0.709677</t>
+  </si>
+  <si>
+    <t>1.870968</t>
+  </si>
+  <si>
+    <t>这条视频我一个字没写｜AI 团队抢着把活干完了 做了 20 年互联网，现在自己创业。
+这条视频，我一个字没写、全程没动手——我就发了一句话，然后去喝了杯水。
+回来一看，活全干完了：我那套系统里，一群 AI 各管一摊，定选题、写脚本、找素材、剪辑、配文案，分工跑完。
+画面里吵吵闹闹的样子，是我把真实流程画出来给你看，不是编故事。
+我做的只有最后点个头。换以前找外包，动不动好几百起、磨好几天、还来回改。
+AI 早不只是帮你写两句了，它更像一支替你干活的团队，你是那个拍板的人。
+你正在看的这条，就是它做的。 
+#一人公司  #AI工具  #流程自动化  #独立开发  #AIGC</t>
+  </si>
+  <si>
+    <t>2026-06-29 13:13:00</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>0.035714</t>
+  </si>
+  <si>
+    <t>0.233333</t>
+  </si>
+  <si>
+    <t>0.600000</t>
+  </si>
+  <si>
+    <t>4.300000</t>
+  </si>
+  <si>
+    <t>小老板最该自动化的，是人走了不会断的那几步 不是先搞营销自动化。先把人走了就断、一忙就漏的那几步拎出来。 
+#小老板  #创业  #自动化  #流程管理  #干货</t>
+  </si>
+  <si>
+    <t>2026-06-27 09:13:00</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>0.163934</t>
+  </si>
+  <si>
+    <t>0.491803</t>
+  </si>
+  <si>
+    <t>3.622951</t>
+  </si>
+  <si>
+    <t>3人电商，退货对账对到差800块找不到 退货量不大，信息在三套系统里，人工对账每月耗两天，差800找不到。
+#电商创业   #退货   #对账   #小公司   #淘宝运营</t>
+  </si>
+  <si>
+    <t>2026-06-26 09:13:00</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>0.019608</t>
+  </si>
+  <si>
+    <t>0.292453</t>
+  </si>
+  <si>
+    <t>0.415094</t>
+  </si>
+  <si>
+    <t>6.415094</t>
   </si>
   <si>
     <t>电商老板做私域，AI agent先接这3件事 私域最耗人的，不是发更多消息，是每天要盯、但一忙就漏的客户节点。
@@ -73,31 +279,16 @@
     <t>2026-06-25 19:20:00</t>
   </si>
   <si>
-    <t>1min-视频</t>
-  </si>
-  <si>
-    <t>公开</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>0.000000</t>
-  </si>
-  <si>
-    <t>0.100000</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0.300000</t>
-  </si>
-  <si>
-    <t>3.500000</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>37</t>
+  </si>
+  <si>
+    <t>0.212121</t>
+  </si>
+  <si>
+    <t>0.424242</t>
+  </si>
+  <si>
+    <t>4.515152</t>
   </si>
   <si>
     <t>300个老客户，复购全靠Excel记 不是卖课，是我帮一个小团队改复购提醒的过程。**不讲功效**，只讲第25天该触达别靠人记。 
@@ -110,16 +301,16 @@
     <t>2026-06-25 09:13:00</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>0.041667</t>
-  </si>
-  <si>
-    <t>0.583333</t>
-  </si>
-  <si>
-    <t>2.208333</t>
+    <t>40</t>
+  </si>
+  <si>
+    <t>0.097561</t>
+  </si>
+  <si>
+    <t>0.487805</t>
+  </si>
+  <si>
+    <t>2.804878</t>
   </si>
   <si>
     <t>186份试吃发出去了，能说出谁反馈的不到20个 不是卖课，是我帮一个小团队改试吃跟进的过程。**不讲功效**，只讲怎么把反馈从三个群里拎出来。 
@@ -132,19 +323,19 @@
     <t>2026-06-24 09:35:00</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>0.243243</t>
-  </si>
-  <si>
-    <t>0.513514</t>
-  </si>
-  <si>
-    <t>3.405405</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>41</t>
+  </si>
+  <si>
+    <t>0.229167</t>
+  </si>
+  <si>
+    <t>0.458333</t>
+  </si>
+  <si>
+    <t>3.333333</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>帮20桌小馆改团购跟进：218单卖了，回访还是0 这条不是卖课，是我帮一家20桌家常菜馆改团购跟进的真实过程。 
@@ -159,16 +350,16 @@
     <t>2026-06-23 09:35:00</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>0.296296</t>
-  </si>
-  <si>
-    <t>0.592593</t>
-  </si>
-  <si>
-    <t>5.629630</t>
+    <t>34</t>
+  </si>
+  <si>
+    <t>0.303030</t>
+  </si>
+  <si>
+    <t>0.575758</t>
+  </si>
+  <si>
+    <t>8.909091</t>
   </si>
   <si>
     <t>美甲店5个微信接单：不是缺表，是缺一条链 不是教程，是我帮一家3技师社区店改预约的过程。**不推销系统**，只讲怎么把烦人的重复活跑通。 
@@ -181,19 +372,16 @@
     <t>1-3min视频</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>0.193548</t>
-  </si>
-  <si>
-    <t>0.677419</t>
-  </si>
-  <si>
-    <t>3.612903</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>49</t>
+  </si>
+  <si>
+    <t>0.195652</t>
+  </si>
+  <si>
+    <t>0.652174</t>
+  </si>
+  <si>
+    <t>4.000000</t>
   </si>
   <si>
     <t>我用claude做了一个短视频内容引擎。原来做一条视频要自己写脚本，找素材。现在好了，抛出一个话题，一群专家agent帮我分析，找素材，做视频。一人公司指日可待。 
@@ -206,19 +394,16 @@
     <t>图文</t>
   </si>
   <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>0.015152</t>
-  </si>
-  <si>
-    <t>0.028571</t>
-  </si>
-  <si>
-    <t>0.557143</t>
-  </si>
-  <si>
-    <t>2.471429</t>
+    <t>80</t>
+  </si>
+  <si>
+    <t>0.012987</t>
+  </si>
+  <si>
+    <t>0.530864</t>
+  </si>
+  <si>
+    <t>2.629630</t>
   </si>
   <si>
     <t>让员工回?他比你还烦。我换了个思路 开店的老板都懂——
@@ -230,16 +415,16 @@
     <t>2026-06-21 10:45:00</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>0.203704</t>
-  </si>
-  <si>
-    <t>0.629630</t>
-  </si>
-  <si>
-    <t>3.833333</t>
+    <t>58</t>
+  </si>
+  <si>
+    <t>0.192982</t>
+  </si>
+  <si>
+    <t>0.631579</t>
+  </si>
+  <si>
+    <t>3.771930</t>
   </si>
   <si>
     <t>测试各种场景下的多agent协调--带货视频 纯agent自动化生成只给了一个商品链接，全程无参与。
@@ -249,16 +434,16 @@
     <t>2026-06-20 15:30:00</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>0.090909</t>
-  </si>
-  <si>
-    <t>0.545455</t>
-  </si>
-  <si>
-    <t>2.090909</t>
+    <t>16</t>
+  </si>
+  <si>
+    <t>0.133333</t>
+  </si>
+  <si>
+    <t>0.533333</t>
+  </si>
+  <si>
+    <t>2.266667</t>
   </si>
   <si>
     <t>我只说了一个选题，一群 Agent 帮我做事全程无参与 做了 20 年互联网，现在自己创业。 
@@ -279,16 +464,19 @@
     <t>2026-06-20 11:26:06</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>0.414634</t>
-  </si>
-  <si>
-    <t>0.292683</t>
-  </si>
-  <si>
-    <t>6.243902</t>
+    <t>47</t>
+  </si>
+  <si>
+    <t>0.023810</t>
+  </si>
+  <si>
+    <t>0.413043</t>
+  </si>
+  <si>
+    <t>0.282609</t>
+  </si>
+  <si>
+    <t>6.978261</t>
   </si>
   <si>
     <t>我说了一句话，9 个 AI 抢着帮我干 做了 20 年互联网，现在自己创业。 
@@ -311,28 +499,25 @@
     <t>2026-06-19 16:33:23</t>
   </si>
   <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>0.030756</t>
-  </si>
-  <si>
-    <t>0.167589</t>
-  </si>
-  <si>
-    <t>0.469565</t>
-  </si>
-  <si>
-    <t>3.831621</t>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>0.030648</t>
+  </si>
+  <si>
+    <t>0.167061</t>
+  </si>
+  <si>
+    <t>0.469661</t>
+  </si>
+  <si>
+    <t>3.825847</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
     <t>13</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>我谈了5个女朋友，被他们说我是渣男 从2021到现在，Copilot、Cursor、Windsurf、Claude Code、Codex 我挨个用了一遍。一个比一个新，一个比一个会撩，可换到最后我才发现：让你心动的一大把，能陪你把活干完的没几个。
@@ -342,16 +527,13 @@
     <t>2026-06-18 17:26:31</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>0.104167</t>
-  </si>
-  <si>
-    <t>0.812500</t>
-  </si>
-  <si>
-    <t>1.895833</t>
+    <t>0.098039</t>
+  </si>
+  <si>
+    <t>0.823529</t>
+  </si>
+  <si>
+    <t>1.843137</t>
   </si>
   <si>
     <t>一个人做老外生意，跟进邮件我一封没发过 留邮箱的那一刻，后面十天六封跟进信全是系统自己发。我做的不是出图，是把「跟进客户」这件最容易拖的事变成自动跑的小系统，做的还是老外的钱。 
@@ -361,13 +543,16 @@
     <t>2026-06-17 14:35:15</t>
   </si>
   <si>
-    <t>0.166667</t>
-  </si>
-  <si>
-    <t>0.458333</t>
-  </si>
-  <si>
-    <t>3.520833</t>
+    <t>45</t>
+  </si>
+  <si>
+    <t>0.163265</t>
+  </si>
+  <si>
+    <t>0.448980</t>
+  </si>
+  <si>
+    <t>3.510204</t>
   </si>
   <si>
     <t>第5天看数据我傻眼了｜海外品牌邮件获客 帮一个海外小品牌，一天搭完落地页+收邮箱+自动邮件。
@@ -380,19 +565,19 @@
     <t>2026-06-16 15:04:25</t>
   </si>
   <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>0.037433</t>
-  </si>
-  <si>
-    <t>0.286458</t>
-  </si>
-  <si>
-    <t>0.463542</t>
-  </si>
-  <si>
-    <t>4.796875</t>
+    <t>175</t>
+  </si>
+  <si>
+    <t>0.036842</t>
+  </si>
+  <si>
+    <t>0.285714</t>
+  </si>
+  <si>
+    <t>0.464286</t>
+  </si>
+  <si>
+    <t>4.765306</t>
   </si>
   <si>
     <t>#历史回忆碎片 记忆自己的记忆</t>
@@ -422,16 +607,19 @@
     <t>2026-06-09 21:53:08</t>
   </si>
   <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>0.075758</t>
-  </si>
-  <si>
-    <t>3.527778</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>78</t>
+  </si>
+  <si>
+    <t>0.071429</t>
+  </si>
+  <si>
+    <t>0.168831</t>
+  </si>
+  <si>
+    <t>0.597403</t>
+  </si>
+  <si>
+    <t>3.428571</t>
   </si>
   <si>
     <t>AI时代你准备好了吗？ 站在AI的十字路口上，普通人该如何选择
@@ -441,16 +629,16 @@
     <t>2026-05-30 17:11:25</t>
   </si>
   <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>0.111364</t>
-  </si>
-  <si>
-    <t>0.636364</t>
-  </si>
-  <si>
-    <t>2.870455</t>
+    <t>406</t>
+  </si>
+  <si>
+    <t>0.114350</t>
+  </si>
+  <si>
+    <t>0.634529</t>
+  </si>
+  <si>
+    <t>2.876682</t>
   </si>
   <si>
     <t>6</t>
@@ -462,19 +650,19 @@
     <t>2026-05-28 21:40:57</t>
   </si>
   <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>0.055556</t>
-  </si>
-  <si>
-    <t>0.116667</t>
-  </si>
-  <si>
-    <t>0.533333</t>
-  </si>
-  <si>
-    <t>3.750000</t>
+    <t>65</t>
+  </si>
+  <si>
+    <t>0.049180</t>
+  </si>
+  <si>
+    <t>0.117647</t>
+  </si>
+  <si>
+    <t>0.558824</t>
+  </si>
+  <si>
+    <t>3.544118</t>
   </si>
   <si>
     <t>#甜甜的恋爱就这么拍 #真实情侣日常</t>
@@ -493,24 +681,6 @@
   </si>
   <si>
     <t>9.750000</t>
-  </si>
-  <si>
-    <t>专业的人做专业的事。自动漫剧，视频工具#不愧是我 #漫剧 #ai视频</t>
-  </si>
-  <si>
-    <t>2026-03-28 09:19:13</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>0.062500</t>
-  </si>
-  <si>
-    <t>0.734375</t>
-  </si>
-  <si>
-    <t>2.000000</t>
   </si>
 </sst>
 </file>
@@ -877,7 +1047,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <cols>
     <col collapsed="false" hidden="false" max="1" min="1" style="1" width="9.5"/>
@@ -983,27 +1153,27 @@
         <v>26</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
@@ -1012,48 +1182,48 @@
         <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -1062,48 +1232,48 @@
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -1112,148 +1282,148 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
@@ -1262,48 +1432,48 @@
         <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
@@ -1312,48 +1482,48 @@
         <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -1362,48 +1532,48 @@
         <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -1412,48 +1582,48 @@
         <v>19</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>18</v>
@@ -1462,48 +1632,48 @@
         <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>18</v>
@@ -1512,148 +1682,148 @@
         <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
@@ -1662,98 +1832,98 @@
         <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
@@ -1762,98 +1932,98 @@
         <v>19</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
@@ -1862,40 +2032,390 @@
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="H21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L20" s="1" t="s">
+      <c r="J21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="L22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>26</v>
+      <c r="P27" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
